--- a/autumn_recruitment_2025.xlsx
+++ b/autumn_recruitment_2025.xlsx
@@ -15,13 +15,719 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
+  <si>
+    <t>中国工商银行</t>
+  </si>
+  <si>
+    <t>星辰管培生/科技菁英/客户经理/客服经理</t>
+  </si>
+  <si>
+    <t>金融</t>
+  </si>
+  <si>
+    <t>全国</t>
+  </si>
+  <si>
+    <t>本科及以上</t>
+  </si>
+  <si>
+    <t>不限（科技岗优先理工类）</t>
+  </si>
+  <si>
+    <t>http://job.icbc.com.cn</t>
+  </si>
+  <si>
+    <t>2025-09-05</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>银行招聘网/东吴教育</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>笔试时间：2025年11月初</t>
+  </si>
+  <si>
+    <t>已截止</t>
+  </si>
+  <si>
+    <t>中国农业银行</t>
+  </si>
+  <si>
+    <t>省分行本部岗/城区业务岗/乡村振兴岗/信息科技岗</t>
+  </si>
+  <si>
+    <t>本科及以上（个别地区大专）</t>
+  </si>
+  <si>
+    <t>不限</t>
+  </si>
+  <si>
+    <t>http://career.abchina.com</t>
+  </si>
+  <si>
+    <t>笔试时间：初定2025年11月</t>
+  </si>
+  <si>
+    <t>中国银行</t>
+  </si>
+  <si>
+    <t>管理培训生/信息科技岗/营业网点业务岗</t>
+  </si>
+  <si>
+    <t>http://campus.chinahr.com/pages/2026-boc</t>
+  </si>
+  <si>
+    <t>2025-10-10</t>
+  </si>
+  <si>
+    <t>笔试时间：9月下旬至10月分批</t>
+  </si>
+  <si>
+    <t>中国建设银行</t>
+  </si>
+  <si>
+    <t>科技类专项人才/综合营销岗/柜面服务岗/管理培训生</t>
+  </si>
+  <si>
+    <t>http://job.ccb.com</t>
+  </si>
+  <si>
+    <t>2025-09-09</t>
+  </si>
+  <si>
+    <t>中国建设银行官网</t>
+  </si>
+  <si>
+    <t>笔试时间：2025年11月初；上海分行招聘450人</t>
+  </si>
+  <si>
+    <t>交通银行</t>
+  </si>
+  <si>
+    <t>管理储备生/科技金融客户经理/养老金融客户经理/营运方向/营销方向/金融科技方向</t>
+  </si>
+  <si>
+    <t>http://job.bankcomm.com</t>
+  </si>
+  <si>
+    <t>2025-10-12</t>
+  </si>
+  <si>
+    <t>可申请金融科技职位、总行应届生职位</t>
+  </si>
+  <si>
+    <t>中国邮政储蓄银行</t>
+  </si>
+  <si>
+    <t>客户服务经理/柜员（定向）/U培生</t>
+  </si>
+  <si>
+    <t>http://psbc.zhaopin.com</t>
+  </si>
+  <si>
+    <t>2025-09-01</t>
+  </si>
+  <si>
+    <t>2025-09-30</t>
+  </si>
+  <si>
+    <t>银行招聘网/极目新闻</t>
+  </si>
+  <si>
+    <t>U培生包括经营管理、金融科技、金融销售方向</t>
+  </si>
+  <si>
+    <t>招商银行</t>
+  </si>
+  <si>
+    <t>定向培养生/数字金融岗/综合培养生/市场营销岗/运营支持岗</t>
+  </si>
+  <si>
+    <t>全国（上海/福建/山东/新疆/内蒙古/广东/湖北等）</t>
+  </si>
+  <si>
+    <t>http://career.cmbchina.com</t>
+  </si>
+  <si>
+    <t>2025-09-03</t>
+  </si>
+  <si>
+    <t>2025-10-10至2025-11-02（各地不同）</t>
+  </si>
+  <si>
+    <t>各地分行截止时间不同</t>
+  </si>
+  <si>
+    <t>兴业银行</t>
+  </si>
+  <si>
+    <t>金融科技/财富管理/风险管理/综合柜员</t>
+  </si>
+  <si>
+    <t>全国/上海</t>
+  </si>
+  <si>
+    <t>http://cib.zhiye.com</t>
+  </si>
+  <si>
+    <t>2025-09-04</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>兴业期货、兴业消费金融同步招聘</t>
+  </si>
+  <si>
+    <t>浦发银行</t>
+  </si>
+  <si>
+    <t>业务储备生（营销方向）/信息科技岗/业务储备生（综合运营方向）</t>
+  </si>
+  <si>
+    <t>https://job.spdb.com.cn</t>
+  </si>
+  <si>
+    <t>2025-10-16</t>
+  </si>
+  <si>
+    <t>武汉分行招聘</t>
+  </si>
+  <si>
+    <t>广发银行</t>
+  </si>
+  <si>
+    <t>金融科技/综合金融/营销管理/运营支持</t>
+  </si>
+  <si>
+    <t>http://cgbchina.zhiye.com</t>
+  </si>
+  <si>
+    <t>总行截止10月10日；含金融科技类岗位</t>
+  </si>
+  <si>
+    <t>宁波银行</t>
+  </si>
+  <si>
+    <t>总行培训生/金融科技定向生/分行培训生/运营培训生</t>
+  </si>
+  <si>
+    <t>http://zhaopin.nbcb.com.cn</t>
+  </si>
+  <si>
+    <t>2025-09-08</t>
+  </si>
+  <si>
+    <t>2025-11-30</t>
+  </si>
+  <si>
+    <t>线上测评与笔试时间：9月起分批进行</t>
+  </si>
+  <si>
+    <t>徽商银行</t>
+  </si>
+  <si>
+    <t>总行管培生/分行管培生/金融科技岗/综合柜员岗</t>
+  </si>
+  <si>
+    <t>全国（安徽为主）</t>
+  </si>
+  <si>
+    <t>http://rczp.hsbank.com.cn</t>
+  </si>
+  <si>
+    <t>2025-09-02</t>
+  </si>
+  <si>
+    <t>部分岗位同时面向2025届毕业生</t>
+  </si>
+  <si>
+    <t>苏州银行</t>
+  </si>
+  <si>
+    <t>总行管培生/金融科技岗/业务培训生</t>
+  </si>
+  <si>
+    <t>江苏</t>
+  </si>
+  <si>
+    <t>研究生及以上</t>
+  </si>
+  <si>
+    <t>http://hr.suzhoubank.com</t>
+  </si>
+  <si>
+    <t>2025-10-25</t>
+  </si>
+  <si>
+    <t>面试时间：预计2025年11月</t>
+  </si>
+  <si>
+    <t>中信证券</t>
+  </si>
+  <si>
+    <t>AI/QUANT/FinTech/投行/研究分析/投资交易/风控合规/财务审计</t>
+  </si>
+  <si>
+    <t>深圳/上海/北京</t>
+  </si>
+  <si>
+    <t>硕士及以上（核心岗）</t>
+  </si>
+  <si>
+    <t>金融/经济/理工/计算机等</t>
+  </si>
+  <si>
+    <t>https://www.citics.com/career</t>
+  </si>
+  <si>
+    <t>招满为止</t>
+  </si>
+  <si>
+    <t>中信证券官网/北京本地宝</t>
+  </si>
+  <si>
+    <t>2025上半年薪酬总额111.23亿元</t>
+  </si>
+  <si>
+    <t>华泰证券</t>
+  </si>
+  <si>
+    <t>财富管理/国际业务/机构服务/投资管理/职能支持</t>
+  </si>
+  <si>
+    <t>硕士及以上</t>
+  </si>
+  <si>
+    <t>https://www.htsc.com.cn/career</t>
+  </si>
+  <si>
+    <t>财联社</t>
+  </si>
+  <si>
+    <t>总部及分支机构共上百个职位</t>
+  </si>
+  <si>
+    <t>东方财富</t>
+  </si>
+  <si>
+    <t>AI产品/互联网产品/AI数据分析/AI金融研究/战略研究/金融机构客户经理</t>
+  </si>
+  <si>
+    <t>金融/计算机/数学/统计等</t>
+  </si>
+  <si>
+    <t>https://eastmoney.zhiye.com</t>
+  </si>
+  <si>
+    <t>金曦计划：EASTstar管培之星+EASTtech科技新锐；共83个岗位</t>
+  </si>
+  <si>
+    <t>广发证券</t>
+  </si>
+  <si>
+    <t>量化开发工程师/AI算法工程师/大数据开发工程师/金融科技产品经理</t>
+  </si>
+  <si>
+    <t>https://gf.zhiye.com</t>
+  </si>
+  <si>
+    <t>2025-09-20</t>
+  </si>
+  <si>
+    <t>金融科技Fintech校园招聘专场；同步推出Quant&amp;AI挑战赛</t>
+  </si>
+  <si>
+    <t>申万宏源</t>
+  </si>
+  <si>
+    <t>财富顾问（分支机构重点岗位）</t>
+  </si>
+  <si>
+    <t>金融/经济/管理类</t>
+  </si>
+  <si>
+    <t>https://www.swhysc.com/career</t>
+  </si>
+  <si>
+    <t>分支机构将财富管理人才作为招聘重点</t>
+  </si>
+  <si>
+    <t>中国中信金融资产管理</t>
+  </si>
+  <si>
+    <t>业务开发岗/法律合规岗/财务岗/审计岗/综合文秘岗</t>
+  </si>
+  <si>
+    <t>北京/杭州/长沙/深圳</t>
+  </si>
+  <si>
+    <t>工商管理/经济/金融/法学/新闻传播</t>
+  </si>
+  <si>
+    <t>https://campus.51job.com/zxjrzc2026</t>
+  </si>
+  <si>
+    <t>2025-09-18</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>高校人才网</t>
+  </si>
+  <si>
+    <t>每人限报2个岗位；流程含性格测试和专业笔试</t>
+  </si>
+  <si>
+    <t>泰康人寿</t>
+  </si>
+  <si>
+    <t>保险管理类/产品销售类/医疗健康类/科技运营类/职能管理类</t>
+  </si>
+  <si>
+    <t>https://jobtaikang.zhiye.com</t>
+  </si>
+  <si>
+    <t>2025-10-01</t>
+  </si>
+  <si>
+    <t>Gankinterview校招汇总</t>
+  </si>
+  <si>
+    <t>秋招补录阶段</t>
+  </si>
+  <si>
+    <t>瑞众保险</t>
+  </si>
+  <si>
+    <t>销售管理/产品精算/信息科技/财务管理/投资管理/纪检审计/综合行政</t>
+  </si>
+  <si>
+    <t>北京/全国</t>
+  </si>
+  <si>
+    <t>金融/保险/精算/财务/计算机等</t>
+  </si>
+  <si>
+    <t>https://ruiinsurance.zhiye.com</t>
+  </si>
+  <si>
+    <t>含分支机构岗位和子公司岗位</t>
+  </si>
+  <si>
+    <t>辉瑞中国</t>
+  </si>
+  <si>
+    <t>管理培训生（市场/销售/战略与业务发展/市场准入/医学部等轮岗）</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>北京/上海</t>
+  </si>
+  <si>
+    <t>专业不限</t>
+  </si>
+  <si>
+    <t>https://careersite.tupu360.com/pfizercampus</t>
+  </si>
+  <si>
+    <t>2025-09-12</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>兰州大学就业网</t>
+  </si>
+  <si>
+    <t>36个月跨职能轮岗；定岗级别为助理经理或经理</t>
+  </si>
+  <si>
+    <t>联合利华</t>
+  </si>
+  <si>
+    <t>销售英才（饮食策划/家庭护理/美妆及个人护理）</t>
+  </si>
+  <si>
+    <t>https://young.yingjiesheng.com</t>
+  </si>
+  <si>
+    <t>2026-01-31</t>
+  </si>
+  <si>
+    <t>面向2023-2026届毕业生</t>
+  </si>
+  <si>
+    <t>泸州老窖</t>
+  </si>
+  <si>
+    <t>金融岗/供应链管理岗/运营管理岗/市场营销岗/投后运营岗/审计岗/法务岗/资产管理岗/财务岗/人力资源岗</t>
+  </si>
+  <si>
+    <t>战略</t>
+  </si>
+  <si>
+    <t>成都/泸州/全国</t>
+  </si>
+  <si>
+    <t>金融/经济/管理/财务/法学等</t>
+  </si>
+  <si>
+    <t>http://campus.51job.com/lzljjt2026</t>
+  </si>
+  <si>
+    <t>国企；含金融岗、运营管理岗、投后运营岗等</t>
+  </si>
+  <si>
+    <t>不凡帝范梅勒</t>
+  </si>
+  <si>
+    <t>销售领英培训生/市场管理培训生/电子商务管理培训生/供应链管理培训生/财务管理培训生/人力资源管理培训生</t>
+  </si>
+  <si>
+    <t>上海/深圳/全国</t>
+  </si>
+  <si>
+    <t>http://campus.51job.com/perfettivanmelle</t>
+  </si>
+  <si>
+    <t>2025-10-21</t>
+  </si>
+  <si>
+    <t>外企快消；面向2025届、2026届</t>
+  </si>
+  <si>
+    <t>优衣库</t>
+  </si>
+  <si>
+    <t>经营管理培训生（UMC）</t>
+  </si>
+  <si>
+    <t>https://uniqlo.zhiye.com</t>
+  </si>
+  <si>
+    <t>大参林</t>
+  </si>
+  <si>
+    <t>MT-集团管培生（营运类/商品类/新零售类/商业分析）</t>
+  </si>
+  <si>
+    <t>商分</t>
+  </si>
+  <si>
+    <t>广州/全国</t>
+  </si>
+  <si>
+    <t>https://dashenlin.zhiye.com</t>
+  </si>
+  <si>
+    <t>含商业分析方向</t>
+  </si>
+  <si>
+    <t>腾讯IEG</t>
+  </si>
+  <si>
+    <t>游戏引擎开发</t>
+  </si>
+  <si>
+    <t>深圳/上海/广州</t>
+  </si>
+  <si>
+    <t>计算机相关</t>
+  </si>
+  <si>
+    <t>https://join.qq.com</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>招满即止</t>
+  </si>
+  <si>
+    <t>鲸推求职/搜狐</t>
+  </si>
+  <si>
+    <t>2027届秋招提前批</t>
+  </si>
+  <si>
+    <t>开放中</t>
+  </si>
+  <si>
+    <t>科大讯飞</t>
+  </si>
+  <si>
+    <t>飞凡计划-研发/产品/营销多方向</t>
+  </si>
+  <si>
+    <t>产品</t>
+  </si>
+  <si>
+    <t>合肥</t>
+  </si>
+  <si>
+    <t>https://campus.iflytek.com</t>
+  </si>
+  <si>
+    <t>2027届秋招提前批；面向2025-2027届</t>
+  </si>
+  <si>
+    <t>拜耳</t>
+  </si>
+  <si>
+    <t>AI工程师/AI产品管理</t>
+  </si>
+  <si>
+    <t>硕士/博士</t>
+  </si>
+  <si>
+    <t>计算机/AI/医药相关</t>
+  </si>
+  <si>
+    <t>https://career.bayer.com.cn</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2027届秋招提前批；面向2026.7-2027.6在读硕博</t>
+  </si>
+  <si>
+    <t>宇通集团</t>
+  </si>
+  <si>
+    <t>财经管培生（财菁计划）</t>
+  </si>
+  <si>
+    <t>郑州</t>
+  </si>
+  <si>
+    <t>本科/硕士</t>
+  </si>
+  <si>
+    <t>财经类</t>
+  </si>
+  <si>
+    <t>https://yutong.zhiye.com</t>
+  </si>
+  <si>
+    <t>朴朴</t>
+  </si>
+  <si>
+    <t>营运管培生</t>
+  </si>
+  <si>
+    <t>运营</t>
+  </si>
+  <si>
+    <t>福州/厦门/深圳/广州/武汉/成都</t>
+  </si>
+  <si>
+    <t>https://pupumall.zhiye.com</t>
+  </si>
+  <si>
+    <t>度小满</t>
+  </si>
+  <si>
+    <t>小满摘星计划-AI实习岗</t>
+  </si>
+  <si>
+    <t>北京/杭州/深圳</t>
+  </si>
+  <si>
+    <t>本硕博在校生</t>
+  </si>
+  <si>
+    <t>计算机/AI/金融相关</t>
+  </si>
+  <si>
+    <t>https://www.duxiaoman.com/campus</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2027届秋招提前批；金融科技方向</t>
+  </si>
+  <si>
+    <t>中国航天科技集团</t>
+  </si>
+  <si>
+    <t>人工智能/集成电路/计算机等方向</t>
+  </si>
+  <si>
+    <t>北京/上海/西安/成都/保定</t>
+  </si>
+  <si>
+    <t>人工智能/集成电路/计算机等</t>
+  </si>
+  <si>
+    <t>https://calt.zhaopin.com</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>中国一汽</t>
+  </si>
+  <si>
+    <t>智能网联/整车/新能源/数智化/智能制造研发</t>
+  </si>
+  <si>
+    <t>长春/北京/天津/上海/无锡/青岛/成都</t>
+  </si>
+  <si>
+    <t>车辆工程/计算机/自动化等</t>
+  </si>
+  <si>
+    <t>https://faw-zhaopin.com</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>索尼</t>
+  </si>
+  <si>
+    <t>云AI实习生/人机交互实习生/交互内容开发实习生</t>
+  </si>
+  <si>
+    <t>计算机/AI相关</t>
+  </si>
+  <si>
+    <t>https://sony.wd5.myworkdayjobs.com</t>
+  </si>
+  <si>
+    <t>飞猪（阿里星）</t>
+  </si>
+  <si>
+    <t>多模态大模型/AI智能体研发</t>
+  </si>
+  <si>
+    <t>杭州</t>
+  </si>
+  <si>
+    <t>https://talent.alibaba.com</t>
+  </si>
+  <si>
+    <t>2027届秋招提前批；阿里星顶尖人才计划</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +735,24 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,8 +767,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+      <alignment/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="false"/>
@@ -439,7 +1159,7 @@
     <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="15"/>
@@ -457,70 +1177,1587 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>公司名称</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>岗位名称</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>岗位类别</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>工作地点</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>学历要求</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>专业要求</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>投递方式/链接</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>开始时间</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>截止时间</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>信息来源</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>收集日期</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" t="s">
+        <v>69</v>
+      </c>
+      <c r="J12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" t="s">
+        <v>70</v>
+      </c>
+      <c r="M12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" t="s">
+        <v>76</v>
+      </c>
+      <c r="M13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" t="s">
+        <v>83</v>
+      </c>
+      <c r="M14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" t="s">
+        <v>90</v>
+      </c>
+      <c r="J15" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" t="s">
+        <v>92</v>
+      </c>
+      <c r="M15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" t="s">
+        <v>90</v>
+      </c>
+      <c r="J16" t="s">
+        <v>97</v>
+      </c>
+      <c r="K16" t="s">
+        <v>10</v>
+      </c>
+      <c r="L16" t="s">
+        <v>98</v>
+      </c>
+      <c r="M16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J17" t="s">
+        <v>97</v>
+      </c>
+      <c r="K17" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" t="s">
+        <v>103</v>
+      </c>
+      <c r="M17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H18" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" t="s">
+        <v>90</v>
+      </c>
+      <c r="J18" t="s">
+        <v>97</v>
+      </c>
+      <c r="K18" t="s">
+        <v>10</v>
+      </c>
+      <c r="L18" t="s">
+        <v>108</v>
+      </c>
+      <c r="M18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" t="s">
+        <v>111</v>
+      </c>
+      <c r="G19" t="s">
+        <v>112</v>
+      </c>
+      <c r="H19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19" t="s">
+        <v>90</v>
+      </c>
+      <c r="J19" t="s">
+        <v>97</v>
+      </c>
+      <c r="K19" t="s">
+        <v>10</v>
+      </c>
+      <c r="L19" t="s">
+        <v>113</v>
+      </c>
+      <c r="M19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" t="s">
+        <v>119</v>
+      </c>
+      <c r="I20" t="s">
+        <v>120</v>
+      </c>
+      <c r="J20" t="s">
+        <v>121</v>
+      </c>
+      <c r="K20" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" t="s">
+        <v>122</v>
+      </c>
+      <c r="M20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" t="s">
+        <v>90</v>
+      </c>
+      <c r="J21" t="s">
+        <v>127</v>
+      </c>
+      <c r="K21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" t="s">
+        <v>128</v>
+      </c>
+      <c r="M21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" t="s">
+        <v>130</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22" t="s">
+        <v>133</v>
+      </c>
+      <c r="H22" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" t="s">
+        <v>90</v>
+      </c>
+      <c r="J22" t="s">
+        <v>127</v>
+      </c>
+      <c r="K22" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" t="s">
+        <v>134</v>
+      </c>
+      <c r="M22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" t="s">
+        <v>140</v>
+      </c>
+      <c r="H23" t="s">
+        <v>141</v>
+      </c>
+      <c r="I23" t="s">
+        <v>142</v>
+      </c>
+      <c r="J23" t="s">
+        <v>143</v>
+      </c>
+      <c r="K23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L23" t="s">
+        <v>144</v>
+      </c>
+      <c r="M23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" t="s">
+        <v>147</v>
+      </c>
+      <c r="H24" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" t="s">
+        <v>148</v>
+      </c>
+      <c r="J24" t="s">
+        <v>127</v>
+      </c>
+      <c r="K24" t="s">
+        <v>10</v>
+      </c>
+      <c r="L24" t="s">
+        <v>149</v>
+      </c>
+      <c r="M24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" t="s">
+        <v>151</v>
+      </c>
+      <c r="C25" t="s">
+        <v>152</v>
+      </c>
+      <c r="D25" t="s">
+        <v>153</v>
+      </c>
+      <c r="E25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" t="s">
+        <v>154</v>
+      </c>
+      <c r="G25" t="s">
+        <v>155</v>
+      </c>
+      <c r="H25" t="s">
+        <v>39</v>
+      </c>
+      <c r="I25" t="s">
+        <v>54</v>
+      </c>
+      <c r="J25" t="s">
+        <v>127</v>
+      </c>
+      <c r="K25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L25" t="s">
+        <v>156</v>
+      </c>
+      <c r="M25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>157</v>
+      </c>
+      <c r="B26" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" t="s">
+        <v>159</v>
+      </c>
+      <c r="E26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" t="s">
+        <v>160</v>
+      </c>
+      <c r="H26" t="s">
+        <v>161</v>
+      </c>
+      <c r="I26" t="s">
+        <v>69</v>
+      </c>
+      <c r="J26" t="s">
+        <v>127</v>
+      </c>
+      <c r="K26" t="s">
+        <v>10</v>
+      </c>
+      <c r="L26" t="s">
+        <v>162</v>
+      </c>
+      <c r="M26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" t="s">
+        <v>139</v>
+      </c>
+      <c r="G27" t="s">
+        <v>165</v>
+      </c>
+      <c r="H27" t="s">
+        <v>126</v>
+      </c>
+      <c r="I27" t="s">
+        <v>90</v>
+      </c>
+      <c r="J27" t="s">
+        <v>127</v>
+      </c>
+      <c r="K27" t="s">
+        <v>10</v>
+      </c>
+      <c r="L27" t="s">
+        <v>162</v>
+      </c>
+      <c r="M27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>166</v>
+      </c>
+      <c r="B28" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" t="s">
+        <v>168</v>
+      </c>
+      <c r="D28" t="s">
+        <v>169</v>
+      </c>
+      <c r="E28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" t="s">
+        <v>170</v>
+      </c>
+      <c r="H28" t="s">
+        <v>126</v>
+      </c>
+      <c r="I28" t="s">
+        <v>90</v>
+      </c>
+      <c r="J28" t="s">
+        <v>127</v>
+      </c>
+      <c r="K28" t="s">
+        <v>10</v>
+      </c>
+      <c r="L28" t="s">
+        <v>171</v>
+      </c>
+      <c r="M28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>172</v>
+      </c>
+      <c r="B29" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" t="s">
+        <v>175</v>
+      </c>
+      <c r="G29" t="s">
+        <v>176</v>
+      </c>
+      <c r="H29" t="s">
+        <v>177</v>
+      </c>
+      <c r="I29" t="s">
+        <v>178</v>
+      </c>
+      <c r="J29" t="s">
+        <v>179</v>
+      </c>
+      <c r="K29" t="s">
+        <v>10</v>
+      </c>
+      <c r="L29" t="s">
+        <v>180</v>
+      </c>
+      <c r="M29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>182</v>
+      </c>
+      <c r="B30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C30" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" t="s">
+        <v>185</v>
+      </c>
+      <c r="E30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" t="s">
+        <v>186</v>
+      </c>
+      <c r="H30" t="s">
+        <v>177</v>
+      </c>
+      <c r="I30" t="s">
+        <v>178</v>
+      </c>
+      <c r="J30" t="s">
+        <v>179</v>
+      </c>
+      <c r="K30" t="s">
+        <v>10</v>
+      </c>
+      <c r="L30" t="s">
+        <v>187</v>
+      </c>
+      <c r="M30" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>188</v>
+      </c>
+      <c r="B31" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" t="s">
+        <v>184</v>
+      </c>
+      <c r="D31" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" t="s">
+        <v>190</v>
+      </c>
+      <c r="F31" t="s">
+        <v>191</v>
+      </c>
+      <c r="G31" t="s">
+        <v>192</v>
+      </c>
+      <c r="H31" t="s">
+        <v>193</v>
+      </c>
+      <c r="I31" t="s">
+        <v>178</v>
+      </c>
+      <c r="J31" t="s">
+        <v>179</v>
+      </c>
+      <c r="K31" t="s">
+        <v>10</v>
+      </c>
+      <c r="L31" t="s">
+        <v>194</v>
+      </c>
+      <c r="M31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>195</v>
+      </c>
+      <c r="B32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>197</v>
+      </c>
+      <c r="E32" t="s">
+        <v>198</v>
+      </c>
+      <c r="F32" t="s">
+        <v>199</v>
+      </c>
+      <c r="G32" t="s">
+        <v>200</v>
+      </c>
+      <c r="H32" t="s">
+        <v>177</v>
+      </c>
+      <c r="I32" t="s">
+        <v>178</v>
+      </c>
+      <c r="J32" t="s">
+        <v>179</v>
+      </c>
+      <c r="K32" t="s">
+        <v>10</v>
+      </c>
+      <c r="L32" t="s">
+        <v>180</v>
+      </c>
+      <c r="M32" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>201</v>
+      </c>
+      <c r="B33" t="s">
+        <v>202</v>
+      </c>
+      <c r="C33" t="s">
+        <v>203</v>
+      </c>
+      <c r="D33" t="s">
+        <v>204</v>
+      </c>
+      <c r="E33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" t="s">
+        <v>205</v>
+      </c>
+      <c r="H33" t="s">
+        <v>177</v>
+      </c>
+      <c r="I33" t="s">
+        <v>178</v>
+      </c>
+      <c r="J33" t="s">
+        <v>179</v>
+      </c>
+      <c r="K33" t="s">
+        <v>10</v>
+      </c>
+      <c r="L33" t="s">
+        <v>180</v>
+      </c>
+      <c r="M33" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>206</v>
+      </c>
+      <c r="B34" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>208</v>
+      </c>
+      <c r="E34" t="s">
+        <v>209</v>
+      </c>
+      <c r="F34" t="s">
+        <v>210</v>
+      </c>
+      <c r="G34" t="s">
+        <v>211</v>
+      </c>
+      <c r="H34" t="s">
+        <v>212</v>
+      </c>
+      <c r="I34" t="s">
+        <v>178</v>
+      </c>
+      <c r="J34" t="s">
+        <v>179</v>
+      </c>
+      <c r="K34" t="s">
+        <v>10</v>
+      </c>
+      <c r="L34" t="s">
+        <v>213</v>
+      </c>
+      <c r="M34" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>214</v>
+      </c>
+      <c r="B35" t="s">
+        <v>215</v>
+      </c>
+      <c r="C35" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35" t="s">
+        <v>216</v>
+      </c>
+      <c r="E35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" t="s">
+        <v>217</v>
+      </c>
+      <c r="G35" t="s">
+        <v>218</v>
+      </c>
+      <c r="H35" t="s">
+        <v>219</v>
+      </c>
+      <c r="I35" t="s">
+        <v>178</v>
+      </c>
+      <c r="J35" t="s">
+        <v>179</v>
+      </c>
+      <c r="K35" t="s">
+        <v>10</v>
+      </c>
+      <c r="L35" t="s">
+        <v>180</v>
+      </c>
+      <c r="M35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>220</v>
+      </c>
+      <c r="B36" t="s">
+        <v>221</v>
+      </c>
+      <c r="C36" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" t="s">
+        <v>222</v>
+      </c>
+      <c r="E36" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" t="s">
+        <v>223</v>
+      </c>
+      <c r="G36" t="s">
+        <v>224</v>
+      </c>
+      <c r="H36" t="s">
+        <v>225</v>
+      </c>
+      <c r="I36" t="s">
+        <v>178</v>
+      </c>
+      <c r="J36" t="s">
+        <v>179</v>
+      </c>
+      <c r="K36" t="s">
+        <v>10</v>
+      </c>
+      <c r="L36" t="s">
+        <v>180</v>
+      </c>
+      <c r="M36" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>226</v>
+      </c>
+      <c r="B37" t="s">
+        <v>227</v>
+      </c>
+      <c r="C37" t="s">
+        <v>137</v>
+      </c>
+      <c r="D37" t="s">
+        <v>138</v>
+      </c>
+      <c r="E37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" t="s">
+        <v>228</v>
+      </c>
+      <c r="G37" t="s">
+        <v>229</v>
+      </c>
+      <c r="H37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I37" t="s">
+        <v>178</v>
+      </c>
+      <c r="J37" t="s">
+        <v>179</v>
+      </c>
+      <c r="K37" t="s">
+        <v>10</v>
+      </c>
+      <c r="L37" t="s">
+        <v>180</v>
+      </c>
+      <c r="M37" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>230</v>
+      </c>
+      <c r="B38" t="s">
+        <v>231</v>
+      </c>
+      <c r="C38" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" t="s">
+        <v>232</v>
+      </c>
+      <c r="E38" t="s">
+        <v>190</v>
+      </c>
+      <c r="F38" t="s">
+        <v>228</v>
+      </c>
+      <c r="G38" t="s">
+        <v>233</v>
+      </c>
+      <c r="H38" t="s">
+        <v>219</v>
+      </c>
+      <c r="I38" t="s">
+        <v>178</v>
+      </c>
+      <c r="J38" t="s">
+        <v>179</v>
+      </c>
+      <c r="K38" t="s">
+        <v>10</v>
+      </c>
+      <c r="L38" t="s">
+        <v>234</v>
+      </c>
+      <c r="M38" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
